--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260604_212449.xlsx
@@ -5856,7 +5856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
